--- a/static/esempio_paziente_completo.xlsx
+++ b/static/esempio_paziente_completo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio Condizioni" sheetId="1" state="visible" r:id="rId3"/>
@@ -4453,10 +4453,10 @@
       <c r="C16" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="12"/>
@@ -6462,10 +6462,10 @@
       <c r="C15" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="57" t="s">
+      <c r="D15" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="57" t="s">
         <v>25</v>
       </c>
     </row>

--- a/static/esempio_paziente_completo.xlsx
+++ b/static/esempio_paziente_completo.xlsx
@@ -21,9 +21,9 @@
     <sheet name="Foglio Mamma" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Base'!$A$2:$H$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Base'!$A$2:$H$61</definedName>
     <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Mamma'!$A$1:$J$29</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Plus'!$A$1:$M$22</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Plus'!$A$1:$M$23</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Sport'!$A$1:$J$28</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Vita'!$A$1:$Q$22</definedName>
   </definedNames>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="227">
   <si>
     <t xml:space="preserve">FOGLIO LAVORO GENEFOOD CONDIZIONI</t>
   </si>
@@ -87,49 +87,157 @@
     <t xml:space="preserve">predisponente</t>
   </si>
   <si>
+    <t xml:space="preserve">ADIPOq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs17300539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1801253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs5082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs662799</t>
+  </si>
+  <si>
     <t xml:space="preserve">APOE</t>
   </si>
   <si>
     <t xml:space="preserve">rs429358</t>
   </si>
   <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
     <t xml:space="preserve">rs7412</t>
   </si>
   <si>
+    <t xml:space="preserve">BDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs6265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CETP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs3764261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs708272</t>
+  </si>
+  <si>
     <t xml:space="preserve">FABP2</t>
   </si>
   <si>
     <t xml:space="preserve">rs1799883</t>
   </si>
   <si>
+    <t xml:space="preserve">FADS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs174546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FADS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs174601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1121980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1421085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1558902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs8050136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs9939609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1799884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs780094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNPDA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs10938397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs11208659</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leptin</t>
   </si>
   <si>
     <t xml:space="preserve">rs7799039</t>
   </si>
   <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADIPOq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs17300539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs9939609</t>
+    <t xml:space="preserve">MC4R </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs17700144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC4R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs17782313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1801131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs1801133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTNR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs10830963</t>
   </si>
   <si>
     <t xml:space="preserve">PPARG</t>
@@ -138,13 +246,10 @@
     <t xml:space="preserve">rs1801282</t>
   </si>
   <si>
-    <t xml:space="preserve">MTHFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1801133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1801131</t>
+    <t xml:space="preserve">SLC30A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs13266634</t>
   </si>
   <si>
     <t xml:space="preserve">TCFL2</t>
@@ -153,99 +258,12 @@
     <t xml:space="preserve">rs7903146</t>
   </si>
   <si>
-    <t xml:space="preserve">GCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1799884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCKR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs780094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC30A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs13266634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTNR1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs10830963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1421085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs5082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC4R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs17782313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs11208659</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMEM18</t>
   </si>
   <si>
     <t xml:space="preserve">rs6548238</t>
   </si>
   <si>
-    <t xml:space="preserve">GNPDA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs10938397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs6265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1801253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FADS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs174601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FADS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs174546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CETP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs3764261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs662799</t>
-  </si>
-  <si>
     <t xml:space="preserve">FOGLIO LAVORO GENEFOOD PLUS</t>
   </si>
   <si>
@@ -264,36 +282,30 @@
     <t xml:space="preserve">rs1800546</t>
   </si>
   <si>
+    <t xml:space="preserve">CLDN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs9290927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs893051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs17501010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYP1A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rs762551</t>
+  </si>
+  <si>
     <t xml:space="preserve">LCT (MCM6)</t>
   </si>
   <si>
     <t xml:space="preserve">rs4988235</t>
   </si>
   <si>
-    <t xml:space="preserve">TNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1800629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs558269137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">del</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYP1A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs762551</t>
-  </si>
-  <si>
     <t xml:space="preserve">HLA_DQA1-B1</t>
   </si>
   <si>
@@ -513,18 +525,6 @@
     <t xml:space="preserve">FOGLIO LAVORO GENEFOOD JUNIOR</t>
   </si>
   <si>
-    <t xml:space="preserve">CLDN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs9290927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs893051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs17501010</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADH1B*2</t>
   </si>
   <si>
@@ -622,12 +622,6 @@
   </si>
   <si>
     <t xml:space="preserve">rs2242670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1121980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs1558902</t>
   </si>
   <si>
     <t xml:space="preserve">rs8050136 </t>
@@ -734,7 +728,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -806,6 +800,38 @@
     </font>
     <font>
       <b val="true"/>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF212121"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF212121"/>
       <name val="Calibri"/>
@@ -830,18 +856,10 @@
     </font>
     <font>
       <b val="true"/>
-      <i val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -890,7 +908,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -930,7 +948,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF33CC33"/>
-        <bgColor rgb="FF33CCCC"/>
+        <bgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF33CC33"/>
       </patternFill>
     </fill>
     <fill>
@@ -1029,7 +1053,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1202,32 +1226,52 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1238,15 +1282,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1258,12 +1302,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1290,51 +1338,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1342,7 +1390,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1422,11 +1470,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1434,39 +1482,39 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1474,59 +1522,59 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1586,7 +1634,7 @@
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF33CC33"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
@@ -1594,7 +1642,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF33CC33"/>
+      <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF212121"/>
       <rgbColor rgb="FF212529"/>
       <rgbColor rgb="FF993300"/>
@@ -1912,7 +1960,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -1931,7 +1979,7 @@
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -1944,12 +1992,12 @@
       <c r="A3" s="5"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="74"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10"/>
     </row>
@@ -1957,89 +2005,89 @@
       <c r="A4" s="5"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="74"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="75"/>
+      <c r="H5" s="81"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="74"/>
+      <c r="H6" s="80"/>
       <c r="I6" s="11"/>
       <c r="J6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="74"/>
+      <c r="H7" s="80"/>
       <c r="I7" s="11"/>
       <c r="J7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="74"/>
+      <c r="H8" s="80"/>
       <c r="I8" s="11"/>
       <c r="J8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="74"/>
+      <c r="H9" s="80"/>
       <c r="I9" s="11"/>
       <c r="J9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="76"/>
+      <c r="H10" s="82"/>
       <c r="I10" s="19"/>
       <c r="J10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="77"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="78"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="19"/>
       <c r="J11" s="18"/>
     </row>
@@ -2047,13 +2095,13 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="85" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="92"/>
+      <c r="F12" s="98"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
@@ -2063,527 +2111,527 @@
       <c r="A13" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="115" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="117" t="s">
+      <c r="B13" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="121" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E13" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="117" t="s">
+      <c r="B14" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E14" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="115" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="115" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="117" t="s">
+      <c r="B15" s="121" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E15" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="115" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="118" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="116" t="s">
+      <c r="B16" s="121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="124" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="123" t="s">
         <v>25</v>
-      </c>
-      <c r="E16" s="117" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="115" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="116" t="s">
+      <c r="B17" s="121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="123" t="s">
         <v>19</v>
-      </c>
-      <c r="E17" s="117" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="115" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="115" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="117" t="s">
-        <v>26</v>
+      <c r="B18" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="121" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="123" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="119" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="119" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="117" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="116" t="s">
-        <v>25</v>
+      <c r="B19" s="125" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="106" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="106" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="117" t="s">
+      <c r="B20" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="122" t="s">
         <v>25</v>
-      </c>
-      <c r="E20" s="116" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="115" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="117" t="s">
-        <v>25</v>
+      <c r="B21" s="121" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="121" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="123" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="115" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="115" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="117" t="s">
+      <c r="B22" s="121" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="121" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E22" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="115" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="115" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="117" t="s">
+      <c r="B23" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E23" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="115" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="115" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="117" t="s">
+      <c r="B24" s="121" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="121" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E24" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="115" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="115" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="117" t="s">
+      <c r="B25" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="121" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E25" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="115" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="115" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="117" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="116" t="s">
-        <v>25</v>
+      <c r="B26" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="121" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="115" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="115" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="117" t="s">
+      <c r="B27" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="121" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E27" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="115" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="117" t="s">
+      <c r="B28" s="121" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="121" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="123" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="122" t="s">
         <v>25</v>
-      </c>
-      <c r="E28" s="116" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="115" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="115" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="117" t="s">
+      <c r="B29" s="121" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="121" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E29" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="118" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="117" t="s">
+      <c r="B30" s="124" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E30" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="115" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="120" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="117" t="s">
+      <c r="B31" s="121" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="122" t="s">
         <v>19</v>
+      </c>
+      <c r="E31" s="123" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="115" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="115" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="117" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="116" t="s">
+      <c r="B32" s="121" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="121" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="123" t="s">
         <v>25</v>
+      </c>
+      <c r="E32" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="115" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="115" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="117" t="s">
+      <c r="B33" s="121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E33" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="115" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="115" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="117" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="116" t="s">
-        <v>25</v>
+      <c r="B34" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="115" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="115" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="121" t="s">
+      <c r="B35" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E35" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="115" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="121" t="s">
+      <c r="B36" s="121" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="122" t="s">
         <v>19</v>
-      </c>
-      <c r="E36" s="116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="115" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="115" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="117" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="116" t="s">
-        <v>25</v>
+      <c r="B37" s="121" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="123" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="115" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="115" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="117" t="s">
+      <c r="B38" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="E38" s="116" t="s">
+      <c r="C38" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="123" t="s">
         <v>25</v>
+      </c>
+      <c r="E38" s="122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="n">
         <v>27</v>
       </c>
-      <c r="B39" s="107" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="106" t="s">
-        <v>195</v>
-      </c>
-      <c r="D39" s="116" t="s">
+      <c r="B39" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="123" t="s">
         <v>25</v>
-      </c>
-      <c r="E39" s="117" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="36" t="n">
         <v>28</v>
       </c>
-      <c r="B40" s="107" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="106" t="s">
-        <v>196</v>
-      </c>
-      <c r="D40" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="117" t="s">
-        <v>26</v>
+      <c r="B40" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="123" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="B41" s="107" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="106" t="s">
-        <v>197</v>
-      </c>
-      <c r="D41" s="116" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="117" t="s">
-        <v>26</v>
+      <c r="B41" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="112" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="123" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="B42" s="106" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="106" t="s">
+      <c r="B42" s="112" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="123" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="116" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" s="128" t="s">
+        <v>197</v>
+      </c>
+      <c r="C43" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="D42" s="116" t="s">
+      <c r="D43" s="129" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="130" t="s">
         <v>25</v>
-      </c>
-      <c r="E42" s="117" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="110" t="n">
-        <v>31</v>
-      </c>
-      <c r="B43" s="122" t="s">
-        <v>199</v>
-      </c>
-      <c r="C43" s="122" t="s">
-        <v>200</v>
-      </c>
-      <c r="D43" s="123" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="124" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2826,7 +2874,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -2850,7 +2898,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -2862,14 +2910,14 @@
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
     </row>
-    <row r="2" s="31" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -2877,98 +2925,114 @@
       <c r="H2" s="30"/>
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="125" t="s">
+      <c r="E3" s="131" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="125" t="s">
+      <c r="E4" s="131" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="125" t="s">
+      <c r="E5" s="131" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="125" t="s">
+      <c r="E6" s="131" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="53"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="131" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="125" t="s">
-        <v>202</v>
+      <c r="E8" s="131" t="s">
+        <v>200</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="125" t="s">
+      <c r="E9" s="131" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="125" t="s">
+      <c r="E10" s="131" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="54"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="125" t="s">
+      <c r="E11" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="77"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
     </row>
@@ -2976,10 +3040,10 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="61" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="37"/>
@@ -2993,20 +3057,20 @@
         <v>1</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="57" t="s">
         <v>19</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>18</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
     </row>
@@ -3015,20 +3079,20 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="38" t="s">
-        <v>205</v>
-      </c>
       <c r="D14" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="57" t="s">
         <v>25</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>22</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14"/>
     </row>
@@ -3037,20 +3101,20 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="62" t="s">
         <v>19</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>18</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
     </row>
@@ -3059,20 +3123,20 @@
         <v>4</v>
       </c>
       <c r="B16" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="38" t="s">
-        <v>208</v>
-      </c>
       <c r="D16" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>22</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14"/>
     </row>
@@ -3081,20 +3145,20 @@
         <v>5</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" s="63" t="s">
         <v>25</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>22</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="15"/>
       <c r="J17" s="14"/>
     </row>
@@ -3103,20 +3167,20 @@
         <v>6</v>
       </c>
       <c r="B18" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="58" t="s">
+      <c r="D18" s="63" t="s">
         <v>19</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>18</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="15"/>
       <c r="J18" s="14"/>
     </row>
@@ -3125,20 +3189,20 @@
         <v>7</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="62" t="s">
         <v>25</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>26</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="15"/>
       <c r="J19" s="14"/>
     </row>
@@ -3147,20 +3211,20 @@
         <v>8</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="58" t="s">
-        <v>18</v>
+        <v>212</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="62" t="s">
+        <v>19</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="15"/>
       <c r="J20" s="14"/>
     </row>
@@ -3169,20 +3233,20 @@
         <v>9</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" s="63" t="s">
         <v>25</v>
+      </c>
+      <c r="E21" s="62" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="15"/>
       <c r="J21" s="14"/>
     </row>
@@ -3191,20 +3255,20 @@
         <v>10</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>217</v>
-      </c>
       <c r="D22" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="57" t="s">
         <v>19</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>18</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="15"/>
       <c r="J22" s="14"/>
     </row>
@@ -3213,20 +3277,20 @@
         <v>11</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="D23" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" s="63" t="s">
         <v>25</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>22</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="58"/>
       <c r="I23" s="15"/>
       <c r="J23" s="14"/>
     </row>
@@ -3235,20 +3299,20 @@
         <v>12</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="62" t="s">
         <v>19</v>
-      </c>
-      <c r="E24" s="58" t="s">
-        <v>18</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="15"/>
       <c r="J24" s="14"/>
     </row>
@@ -3257,20 +3321,20 @@
         <v>13</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="63" t="s">
         <v>25</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>26</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="53"/>
+      <c r="H25" s="58"/>
       <c r="I25" s="15"/>
       <c r="J25" s="14"/>
     </row>
@@ -3279,20 +3343,20 @@
         <v>14</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="57" t="s">
         <v>19</v>
+      </c>
+      <c r="E26" s="63" t="s">
+        <v>18</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="13"/>
-      <c r="H26" s="53"/>
+      <c r="H26" s="58"/>
       <c r="I26" s="15"/>
       <c r="J26" s="14"/>
     </row>
@@ -3301,20 +3365,20 @@
         <v>15</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="D27" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="15"/>
       <c r="J27" s="14"/>
     </row>
@@ -3323,20 +3387,20 @@
         <v>16</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D28" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="63" t="s">
         <v>25</v>
-      </c>
-      <c r="E28" s="57" t="s">
-        <v>26</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="13"/>
-      <c r="H28" s="53"/>
+      <c r="H28" s="58"/>
       <c r="I28" s="15"/>
       <c r="J28" s="14"/>
     </row>
@@ -3345,20 +3409,20 @@
         <v>17</v>
       </c>
       <c r="B29" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="C29" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="D29" s="57" t="s">
-        <v>26</v>
+      <c r="D29" s="63" t="s">
+        <v>25</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
-      <c r="H29" s="53"/>
+      <c r="H29" s="58"/>
       <c r="I29" s="15"/>
       <c r="J29" s="14"/>
     </row>
@@ -3389,7 +3453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:XFD61"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -3443,6 +3507,7 @@
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
@@ -3598,16 +3663,16 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>22</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
@@ -3621,16 +3686,16 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>22</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
@@ -3643,17 +3708,17 @@
       <c r="A16" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="39" t="s">
+      <c r="B16" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>26</v>
+      <c r="E16" s="39" t="s">
+        <v>22</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
@@ -3667,10 +3732,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>19</v>
@@ -3690,16 +3755,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
@@ -3712,17 +3777,17 @@
       <c r="A19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="38" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>25</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
@@ -3735,17 +3800,17 @@
       <c r="A20" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>26</v>
+      <c r="D20" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>19</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
@@ -3758,14 +3823,14 @@
       <c r="A21" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="45" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E21" s="40" t="s">
         <v>25</v>
@@ -3788,10 +3853,10 @@
         <v>37</v>
       </c>
       <c r="D22" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
@@ -3804,17 +3869,17 @@
       <c r="A23" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="42" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
@@ -3827,17 +3892,17 @@
       <c r="A24" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="42" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13"/>
@@ -3850,40 +3915,52 @@
       <c r="A25" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="13"/>
+      <c r="D25" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="0"/>
+      <c r="K25" s="0"/>
+      <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
+      <c r="O25" s="0"/>
+      <c r="P25" s="0"/>
+      <c r="Q25" s="0"/>
+      <c r="R25" s="0"/>
+      <c r="S25" s="0"/>
+      <c r="T25" s="0"/>
+      <c r="U25" s="0"/>
+      <c r="V25" s="0"/>
+      <c r="W25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="n">
         <v>14</v>
       </c>
       <c r="B26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="39" t="s">
-        <v>25</v>
+      <c r="E26" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="13"/>
@@ -3896,63 +3973,87 @@
       <c r="A27" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>46</v>
+      <c r="B27" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>45</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="13"/>
+        <v>25</v>
+      </c>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
+      <c r="I27" s="0"/>
+      <c r="J27" s="0"/>
+      <c r="K27" s="0"/>
+      <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
+      <c r="O27" s="0"/>
+      <c r="P27" s="0"/>
+      <c r="Q27" s="0"/>
+      <c r="R27" s="0"/>
+      <c r="S27" s="0"/>
+      <c r="T27" s="0"/>
+      <c r="U27" s="0"/>
+      <c r="V27" s="0"/>
+      <c r="W27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="39" t="s">
+      <c r="B28" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="13"/>
+      <c r="F28" s="0"/>
+      <c r="G28" s="0"/>
+      <c r="H28" s="0"/>
+      <c r="I28" s="0"/>
+      <c r="J28" s="0"/>
+      <c r="K28" s="0"/>
+      <c r="L28" s="0"/>
+      <c r="M28" s="0"/>
+      <c r="N28" s="0"/>
+      <c r="O28" s="0"/>
+      <c r="P28" s="0"/>
+      <c r="Q28" s="0"/>
+      <c r="R28" s="0"/>
+      <c r="S28" s="0"/>
+      <c r="T28" s="0"/>
+      <c r="U28" s="0"/>
+      <c r="V28" s="0"/>
+      <c r="W28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="n">
         <v>17</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="13"/>
@@ -3965,16 +4066,16 @@
       <c r="A30" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="40" t="s">
+      <c r="B30" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F30" s="12"/>
@@ -3984,20 +4085,20 @@
       <c r="J30" s="12"/>
       <c r="K30" s="13"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="36" t="n">
         <v>19</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F31" s="12"/>
@@ -4012,16 +4113,16 @@
         <v>20</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="13"/>
@@ -4034,16 +4135,16 @@
       <c r="A33" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" s="40" t="s">
+      <c r="B33" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="39" t="s">
+      <c r="E33" s="40" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="12"/>
@@ -4058,15 +4159,15 @@
         <v>22</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="40" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="12"/>
@@ -4080,17 +4181,17 @@
       <c r="A35" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="45" t="s">
-        <v>61</v>
+      <c r="B35" s="46" t="s">
+        <v>58</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="48" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>25</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
@@ -4103,16 +4204,16 @@
       <c r="A36" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="47" t="s">
+      <c r="B36" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="48" t="s">
+      <c r="E36" s="40" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="12"/>
@@ -4126,17 +4227,17 @@
       <c r="A37" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="48" t="s">
-        <v>25</v>
+      <c r="B37" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>22</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="13"/>
@@ -4149,16 +4250,16 @@
       <c r="A38" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="48" t="s">
+      <c r="B38" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="43" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="12"/>
@@ -4167,6 +4268,571 @@
       <c r="I38" s="15"/>
       <c r="J38" s="12"/>
       <c r="K38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="0"/>
+      <c r="C44" s="0"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0"/>
+      <c r="G44" s="0"/>
+      <c r="H44" s="0"/>
+      <c r="I44" s="0"/>
+      <c r="J44" s="0"/>
+      <c r="K44" s="0"/>
+      <c r="L44" s="0"/>
+      <c r="M44" s="0"/>
+      <c r="N44" s="0"/>
+      <c r="O44" s="0"/>
+      <c r="P44" s="0"/>
+      <c r="Q44" s="0"/>
+      <c r="R44" s="0"/>
+      <c r="S44" s="0"/>
+      <c r="T44" s="0"/>
+      <c r="U44" s="0"/>
+      <c r="V44" s="0"/>
+      <c r="W44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0"/>
+      <c r="B45" s="0"/>
+      <c r="C45" s="0"/>
+      <c r="D45" s="0"/>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0"/>
+      <c r="G45" s="0"/>
+      <c r="H45" s="0"/>
+      <c r="I45" s="0"/>
+      <c r="J45" s="0"/>
+      <c r="K45" s="0"/>
+      <c r="L45" s="0"/>
+      <c r="M45" s="0"/>
+      <c r="N45" s="0"/>
+      <c r="O45" s="0"/>
+      <c r="P45" s="0"/>
+      <c r="Q45" s="0"/>
+      <c r="R45" s="0"/>
+      <c r="S45" s="0"/>
+      <c r="T45" s="0"/>
+      <c r="U45" s="0"/>
+      <c r="V45" s="0"/>
+      <c r="W45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="0"/>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0"/>
+      <c r="G46" s="0"/>
+      <c r="H46" s="0"/>
+      <c r="I46" s="0"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
+      <c r="L46" s="0"/>
+      <c r="M46" s="0"/>
+      <c r="N46" s="0"/>
+      <c r="O46" s="0"/>
+      <c r="P46" s="0"/>
+      <c r="Q46" s="0"/>
+      <c r="R46" s="0"/>
+      <c r="S46" s="0"/>
+      <c r="T46" s="0"/>
+      <c r="U46" s="0"/>
+      <c r="V46" s="0"/>
+      <c r="W46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0"/>
+      <c r="B47" s="0"/>
+      <c r="C47" s="0"/>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0"/>
+      <c r="G47" s="0"/>
+      <c r="H47" s="0"/>
+      <c r="I47" s="0"/>
+      <c r="J47" s="0"/>
+      <c r="K47" s="0"/>
+      <c r="L47" s="0"/>
+      <c r="M47" s="0"/>
+      <c r="N47" s="0"/>
+      <c r="O47" s="0"/>
+      <c r="P47" s="0"/>
+      <c r="Q47" s="0"/>
+      <c r="R47" s="0"/>
+      <c r="S47" s="0"/>
+      <c r="T47" s="0"/>
+      <c r="U47" s="0"/>
+      <c r="V47" s="0"/>
+      <c r="W47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0"/>
+      <c r="B48" s="0"/>
+      <c r="C48" s="0"/>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0"/>
+      <c r="G48" s="0"/>
+      <c r="H48" s="0"/>
+      <c r="I48" s="0"/>
+      <c r="J48" s="0"/>
+      <c r="K48" s="0"/>
+      <c r="L48" s="0"/>
+      <c r="M48" s="0"/>
+      <c r="N48" s="0"/>
+      <c r="O48" s="0"/>
+      <c r="P48" s="0"/>
+      <c r="Q48" s="0"/>
+      <c r="R48" s="0"/>
+      <c r="S48" s="0"/>
+      <c r="T48" s="0"/>
+      <c r="U48" s="0"/>
+      <c r="V48" s="0"/>
+      <c r="W48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0"/>
+      <c r="B49" s="0"/>
+      <c r="C49" s="0"/>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0"/>
+      <c r="G49" s="0"/>
+      <c r="H49" s="0"/>
+      <c r="I49" s="0"/>
+      <c r="J49" s="0"/>
+      <c r="K49" s="0"/>
+      <c r="L49" s="0"/>
+      <c r="M49" s="0"/>
+      <c r="N49" s="0"/>
+      <c r="O49" s="0"/>
+      <c r="P49" s="0"/>
+      <c r="Q49" s="0"/>
+      <c r="R49" s="0"/>
+      <c r="S49" s="0"/>
+      <c r="T49" s="0"/>
+      <c r="U49" s="0"/>
+      <c r="V49" s="0"/>
+      <c r="W49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="B50" s="0"/>
+      <c r="C50" s="0"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="0"/>
+      <c r="G50" s="0"/>
+      <c r="H50" s="0"/>
+      <c r="I50" s="0"/>
+      <c r="J50" s="0"/>
+      <c r="K50" s="0"/>
+      <c r="L50" s="0"/>
+      <c r="M50" s="0"/>
+      <c r="N50" s="0"/>
+      <c r="O50" s="0"/>
+      <c r="P50" s="0"/>
+      <c r="Q50" s="0"/>
+      <c r="R50" s="0"/>
+      <c r="S50" s="0"/>
+      <c r="T50" s="0"/>
+      <c r="U50" s="0"/>
+      <c r="V50" s="0"/>
+      <c r="W50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
+      <c r="B51" s="0"/>
+      <c r="C51" s="0"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="0"/>
+      <c r="G51" s="0"/>
+      <c r="H51" s="0"/>
+      <c r="I51" s="0"/>
+      <c r="J51" s="0"/>
+      <c r="K51" s="0"/>
+      <c r="L51" s="0"/>
+      <c r="M51" s="0"/>
+      <c r="N51" s="0"/>
+      <c r="O51" s="0"/>
+      <c r="P51" s="0"/>
+      <c r="Q51" s="0"/>
+      <c r="R51" s="0"/>
+      <c r="S51" s="0"/>
+      <c r="T51" s="0"/>
+      <c r="U51" s="0"/>
+      <c r="V51" s="0"/>
+      <c r="W51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0"/>
+      <c r="B52" s="0"/>
+      <c r="C52" s="0"/>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0"/>
+      <c r="G52" s="0"/>
+      <c r="H52" s="0"/>
+      <c r="I52" s="0"/>
+      <c r="J52" s="0"/>
+      <c r="K52" s="0"/>
+      <c r="L52" s="0"/>
+      <c r="M52" s="0"/>
+      <c r="N52" s="0"/>
+      <c r="O52" s="0"/>
+      <c r="P52" s="0"/>
+      <c r="Q52" s="0"/>
+      <c r="R52" s="0"/>
+      <c r="S52" s="0"/>
+      <c r="T52" s="0"/>
+      <c r="U52" s="0"/>
+      <c r="V52" s="0"/>
+      <c r="W52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0"/>
+      <c r="B53" s="0"/>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+      <c r="G53" s="0"/>
+      <c r="H53" s="0"/>
+      <c r="I53" s="0"/>
+      <c r="J53" s="0"/>
+      <c r="K53" s="0"/>
+      <c r="L53" s="0"/>
+      <c r="M53" s="0"/>
+      <c r="N53" s="0"/>
+      <c r="O53" s="0"/>
+      <c r="P53" s="0"/>
+      <c r="Q53" s="0"/>
+      <c r="R53" s="0"/>
+      <c r="S53" s="0"/>
+      <c r="T53" s="0"/>
+      <c r="U53" s="0"/>
+      <c r="V53" s="0"/>
+      <c r="W53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0"/>
+      <c r="B54" s="0"/>
+      <c r="C54" s="0"/>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0"/>
+      <c r="G54" s="0"/>
+      <c r="H54" s="0"/>
+      <c r="I54" s="0"/>
+      <c r="J54" s="0"/>
+      <c r="K54" s="0"/>
+      <c r="L54" s="0"/>
+      <c r="M54" s="0"/>
+      <c r="N54" s="0"/>
+      <c r="O54" s="0"/>
+      <c r="P54" s="0"/>
+      <c r="Q54" s="0"/>
+      <c r="R54" s="0"/>
+      <c r="S54" s="0"/>
+      <c r="T54" s="0"/>
+      <c r="U54" s="0"/>
+      <c r="V54" s="0"/>
+      <c r="W54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="B55" s="0"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0"/>
+      <c r="G55" s="0"/>
+      <c r="H55" s="0"/>
+      <c r="I55" s="0"/>
+      <c r="J55" s="0"/>
+      <c r="K55" s="0"/>
+      <c r="L55" s="0"/>
+      <c r="M55" s="0"/>
+      <c r="N55" s="0"/>
+      <c r="O55" s="0"/>
+      <c r="P55" s="0"/>
+      <c r="Q55" s="0"/>
+      <c r="R55" s="0"/>
+      <c r="S55" s="0"/>
+      <c r="T55" s="0"/>
+      <c r="U55" s="0"/>
+      <c r="V55" s="0"/>
+      <c r="W55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0"/>
+      <c r="B56" s="0"/>
+      <c r="C56" s="0"/>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0"/>
+      <c r="G56" s="0"/>
+      <c r="H56" s="0"/>
+      <c r="I56" s="0"/>
+      <c r="J56" s="0"/>
+      <c r="K56" s="0"/>
+      <c r="L56" s="0"/>
+      <c r="M56" s="0"/>
+      <c r="N56" s="0"/>
+      <c r="O56" s="0"/>
+      <c r="P56" s="0"/>
+      <c r="Q56" s="0"/>
+      <c r="R56" s="0"/>
+      <c r="S56" s="0"/>
+      <c r="T56" s="0"/>
+      <c r="U56" s="0"/>
+      <c r="V56" s="0"/>
+      <c r="W56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0"/>
+      <c r="B57" s="0"/>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0"/>
+      <c r="G57" s="0"/>
+      <c r="H57" s="0"/>
+      <c r="I57" s="0"/>
+      <c r="J57" s="0"/>
+      <c r="K57" s="0"/>
+      <c r="L57" s="0"/>
+      <c r="M57" s="0"/>
+      <c r="N57" s="0"/>
+      <c r="O57" s="0"/>
+      <c r="P57" s="0"/>
+      <c r="Q57" s="0"/>
+      <c r="R57" s="0"/>
+      <c r="S57" s="0"/>
+      <c r="T57" s="0"/>
+      <c r="U57" s="0"/>
+      <c r="V57" s="0"/>
+      <c r="W57" s="0"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0"/>
+      <c r="B58" s="0"/>
+      <c r="C58" s="0"/>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0"/>
+      <c r="G58" s="0"/>
+      <c r="H58" s="0"/>
+      <c r="I58" s="0"/>
+      <c r="J58" s="0"/>
+      <c r="K58" s="0"/>
+      <c r="L58" s="0"/>
+      <c r="M58" s="0"/>
+      <c r="N58" s="0"/>
+      <c r="O58" s="0"/>
+      <c r="P58" s="0"/>
+      <c r="Q58" s="0"/>
+      <c r="R58" s="0"/>
+      <c r="S58" s="0"/>
+      <c r="T58" s="0"/>
+      <c r="U58" s="0"/>
+      <c r="V58" s="0"/>
+      <c r="W58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0"/>
+      <c r="B59" s="0"/>
+      <c r="C59" s="0"/>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0"/>
+      <c r="G59" s="0"/>
+      <c r="H59" s="0"/>
+      <c r="I59" s="0"/>
+      <c r="J59" s="0"/>
+      <c r="K59" s="0"/>
+      <c r="L59" s="0"/>
+      <c r="M59" s="0"/>
+      <c r="N59" s="0"/>
+      <c r="O59" s="0"/>
+      <c r="P59" s="0"/>
+      <c r="Q59" s="0"/>
+      <c r="R59" s="0"/>
+      <c r="S59" s="0"/>
+      <c r="T59" s="0"/>
+      <c r="U59" s="0"/>
+      <c r="V59" s="0"/>
+      <c r="W59" s="0"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0"/>
+      <c r="B60" s="0"/>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0"/>
+      <c r="G60" s="0"/>
+      <c r="H60" s="0"/>
+      <c r="I60" s="0"/>
+      <c r="J60" s="0"/>
+      <c r="K60" s="0"/>
+      <c r="L60" s="0"/>
+      <c r="M60" s="0"/>
+      <c r="N60" s="0"/>
+      <c r="O60" s="0"/>
+      <c r="P60" s="0"/>
+      <c r="Q60" s="0"/>
+      <c r="R60" s="0"/>
+      <c r="S60" s="0"/>
+      <c r="T60" s="0"/>
+      <c r="U60" s="0"/>
+      <c r="V60" s="0"/>
+      <c r="W60" s="0"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0"/>
+      <c r="B61" s="0"/>
+      <c r="C61" s="0"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0"/>
+      <c r="G61" s="0"/>
+      <c r="H61" s="0"/>
+      <c r="I61" s="0"/>
+      <c r="J61" s="0"/>
+      <c r="K61" s="0"/>
+      <c r="L61" s="0"/>
+      <c r="M61" s="0"/>
+      <c r="N61" s="0"/>
+      <c r="O61" s="0"/>
+      <c r="P61" s="0"/>
+      <c r="Q61" s="0"/>
+      <c r="R61" s="0"/>
+      <c r="S61" s="0"/>
+      <c r="T61" s="0"/>
+      <c r="U61" s="0"/>
+      <c r="V61" s="0"/>
+      <c r="W61" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4195,7 +4861,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -4218,7 +4884,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -4231,14 +4897,14 @@
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
     </row>
-    <row r="2" s="31" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="50"/>
+      <c r="E2" s="55"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -4247,16 +4913,31 @@
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
       <c r="K3" s="12"/>
@@ -4264,89 +4945,89 @@
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
       <c r="K4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
       <c r="K5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="53"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
       <c r="K6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
       <c r="K7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
       <c r="K8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
       <c r="K9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="54"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
       <c r="K10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
       <c r="K11" s="22"/>
@@ -4361,10 +5042,10 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="61" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="37"/>
@@ -4379,20 +5060,20 @@
         <v>1</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="63" t="s">
         <v>25</v>
-      </c>
-      <c r="E13" s="58" t="s">
-        <v>26</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
       <c r="K13" s="12"/>
@@ -4402,20 +5083,20 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="58" t="s">
-        <v>18</v>
+        <v>79</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>19</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14"/>
       <c r="K14" s="12"/>
@@ -4425,20 +5106,20 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>18</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
       <c r="K15" s="12"/>
@@ -4447,116 +5128,139 @@
       <c r="A16" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="57" t="s">
+      <c r="B16" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="63" t="s">
         <v>25</v>
+      </c>
+      <c r="E16" s="62" t="s">
+        <v>19</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14"/>
       <c r="K16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>18</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="15"/>
       <c r="J17" s="14"/>
       <c r="K17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="58" t="s">
-        <v>82</v>
+      <c r="C18" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>19</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="15"/>
       <c r="J18" s="14"/>
       <c r="K18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>26</v>
+        <v>86</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>25</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="15"/>
       <c r="J19" s="14"/>
       <c r="K19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="60" t="s">
+      <c r="C20" s="47" t="s">
         <v>88</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="62" t="s">
+        <v>22</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="15"/>
       <c r="J20" s="14"/>
       <c r="K20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4585,7 +5289,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -4600,7 +5304,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -4619,7 +5323,7 @@
       <c r="P1" s="27"/>
       <c r="Q1" s="27"/>
     </row>
-    <row r="2" s="31" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
@@ -4641,21 +5345,23 @@
       <c r="O2" s="30"/>
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
       <c r="K3" s="12"/>
       <c r="L3" s="13"/>
-      <c r="M3" s="52"/>
+      <c r="M3" s="57"/>
       <c r="N3" s="15"/>
       <c r="O3" s="14"/>
       <c r="P3" s="12"/>
@@ -4664,136 +5370,136 @@
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
-      <c r="M4" s="52"/>
+      <c r="M4" s="57"/>
       <c r="N4" s="15"/>
       <c r="O4" s="14"/>
       <c r="P4" s="12"/>
       <c r="Q4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
       <c r="K5" s="12"/>
       <c r="L5" s="13"/>
-      <c r="M5" s="53"/>
+      <c r="M5" s="58"/>
       <c r="N5" s="15"/>
       <c r="O5" s="14"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="53"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
       <c r="K6" s="8"/>
       <c r="L6" s="13"/>
-      <c r="M6" s="53"/>
+      <c r="M6" s="58"/>
       <c r="N6" s="15"/>
       <c r="O6" s="14"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
       <c r="K7" s="8"/>
       <c r="L7" s="13"/>
-      <c r="M7" s="53"/>
+      <c r="M7" s="58"/>
       <c r="N7" s="15"/>
       <c r="O7" s="14"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
       <c r="K8" s="8"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="53"/>
+      <c r="M8" s="58"/>
       <c r="N8" s="15"/>
       <c r="O8" s="14"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
       <c r="K9" s="8"/>
       <c r="L9" s="13"/>
-      <c r="M9" s="53"/>
+      <c r="M9" s="58"/>
       <c r="N9" s="15"/>
       <c r="O9" s="14"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="54"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
       <c r="K10" s="16"/>
       <c r="L10" s="23"/>
-      <c r="M10" s="54"/>
+      <c r="M10" s="59"/>
       <c r="N10" s="21"/>
       <c r="O10" s="20"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
       <c r="K11" s="16"/>
       <c r="L11" s="23"/>
-      <c r="M11" s="54"/>
+      <c r="M11" s="59"/>
       <c r="N11" s="21"/>
       <c r="O11" s="20"/>
       <c r="P11" s="22"/>
@@ -4803,10 +5509,10 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="61" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="37"/>
@@ -4827,25 +5533,25 @@
         <v>1</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>19</v>
+        <v>95</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>18</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
       <c r="K13" s="12"/>
       <c r="L13" s="13"/>
-      <c r="M13" s="53"/>
+      <c r="M13" s="58"/>
       <c r="N13" s="15"/>
       <c r="O13" s="14"/>
       <c r="P13" s="12"/>
@@ -4856,25 +5562,25 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>25</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>26</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14"/>
       <c r="K14" s="12"/>
       <c r="L14" s="13"/>
-      <c r="M14" s="53"/>
+      <c r="M14" s="58"/>
       <c r="N14" s="15"/>
       <c r="O14" s="14"/>
       <c r="P14" s="12"/>
@@ -4885,25 +5591,25 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D15" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
       <c r="K15" s="12"/>
       <c r="L15" s="13"/>
-      <c r="M15" s="53"/>
+      <c r="M15" s="58"/>
       <c r="N15" s="15"/>
       <c r="O15" s="14"/>
       <c r="P15" s="12"/>
@@ -4914,25 +5620,25 @@
         <v>4</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>99</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14"/>
       <c r="K16" s="12"/>
       <c r="L16" s="13"/>
-      <c r="M16" s="53"/>
+      <c r="M16" s="58"/>
       <c r="N16" s="15"/>
       <c r="O16" s="14"/>
       <c r="P16" s="12"/>
@@ -4942,26 +5648,26 @@
       <c r="A17" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>97</v>
+      <c r="B17" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>101</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="15"/>
       <c r="J17" s="14"/>
       <c r="K17" s="12"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="53"/>
+      <c r="M17" s="58"/>
       <c r="N17" s="15"/>
       <c r="O17" s="14"/>
       <c r="P17" s="12"/>
@@ -4971,26 +5677,26 @@
       <c r="A18" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>18</v>
+      <c r="B18" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>19</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="15"/>
       <c r="J18" s="14"/>
       <c r="K18" s="12"/>
       <c r="L18" s="13"/>
-      <c r="M18" s="53"/>
+      <c r="M18" s="58"/>
       <c r="N18" s="15"/>
       <c r="O18" s="14"/>
       <c r="P18" s="12"/>
@@ -5001,25 +5707,25 @@
         <v>7</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="57" t="s">
-        <v>25</v>
+        <v>104</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>22</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="15"/>
       <c r="J19" s="14"/>
       <c r="K19" s="12"/>
       <c r="L19" s="13"/>
-      <c r="M19" s="53"/>
+      <c r="M19" s="58"/>
       <c r="N19" s="15"/>
       <c r="O19" s="14"/>
       <c r="P19" s="12"/>
@@ -5030,25 +5736,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D20" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="15"/>
       <c r="J20" s="14"/>
       <c r="K20" s="12"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="53"/>
+      <c r="M20" s="58"/>
       <c r="N20" s="15"/>
       <c r="O20" s="14"/>
       <c r="P20" s="12"/>
@@ -5058,26 +5764,26 @@
       <c r="A21" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>34</v>
+      <c r="B21" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>64</v>
       </c>
       <c r="D21" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="39" t="s">
         <v>25</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>26</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="15"/>
       <c r="J21" s="14"/>
       <c r="K21" s="12"/>
       <c r="L21" s="13"/>
-      <c r="M21" s="53"/>
+      <c r="M21" s="58"/>
       <c r="N21" s="15"/>
       <c r="O21" s="14"/>
       <c r="P21" s="12"/>
@@ -5088,45 +5794,45 @@
         <v>10</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="15"/>
       <c r="J22" s="14"/>
       <c r="K22" s="12"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="53"/>
+      <c r="M22" s="58"/>
       <c r="N22" s="15"/>
       <c r="O22" s="14"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="61"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
     </row>
@@ -5157,7 +5863,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -5177,9 +5883,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="15" style="1" width="5.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -5190,15 +5896,30 @@
       <c r="H1" s="27"/>
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
-    </row>
-    <row r="2" s="31" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+    </row>
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -5206,106 +5927,121 @@
       <c r="H2" s="30"/>
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="52"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="53"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="57"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="52"/>
+      <c r="H9" s="57"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="54"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="67" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="37"/>
@@ -5317,20 +6053,20 @@
         <v>1</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
     </row>
@@ -5339,20 +6075,20 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D14" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14"/>
     </row>
@@ -5361,20 +6097,20 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
     </row>
@@ -5383,20 +6119,20 @@
         <v>4</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>111</v>
+        <v>114</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>115</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14"/>
     </row>
@@ -5405,20 +6141,20 @@
         <v>5</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D17" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="15"/>
       <c r="J17" s="14"/>
     </row>
@@ -5427,20 +6163,20 @@
         <v>6</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D18" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="15"/>
       <c r="J18" s="14"/>
     </row>
@@ -5448,21 +6184,21 @@
       <c r="A19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>117</v>
+      <c r="B19" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>121</v>
       </c>
       <c r="D19" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>18</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="15"/>
       <c r="J19" s="14"/>
     </row>
@@ -5470,21 +6206,21 @@
       <c r="A20" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>119</v>
+      <c r="B20" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>123</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="15"/>
       <c r="J20" s="14"/>
     </row>
@@ -5493,20 +6229,20 @@
         <v>9</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="15"/>
       <c r="J21" s="14"/>
     </row>
@@ -5515,20 +6251,20 @@
         <v>10</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="15"/>
       <c r="J22" s="14"/>
     </row>
@@ -5537,20 +6273,20 @@
         <v>11</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D23" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="40" t="s">
         <v>19</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>18</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="58"/>
       <c r="I23" s="15"/>
       <c r="J23" s="14"/>
     </row>
@@ -5559,20 +6295,20 @@
         <v>12</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="40" t="s">
         <v>19</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>18</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="15"/>
       <c r="J24" s="14"/>
     </row>
@@ -5581,20 +6317,20 @@
         <v>13</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="53"/>
+      <c r="H25" s="58"/>
       <c r="I25" s="15"/>
       <c r="J25" s="14"/>
     </row>
@@ -5603,20 +6339,20 @@
         <v>14</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="13"/>
-      <c r="H26" s="53"/>
+      <c r="H26" s="58"/>
       <c r="I26" s="15"/>
       <c r="J26" s="14"/>
     </row>
@@ -5625,20 +6361,20 @@
         <v>15</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="15"/>
       <c r="J27" s="14"/>
     </row>
@@ -5647,76 +6383,76 @@
         <v>16</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="13"/>
-      <c r="H28" s="53"/>
+      <c r="H28" s="58"/>
       <c r="I28" s="15"/>
       <c r="J28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="67"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="67"/>
-      <c r="C32" s="67"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="69"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="72"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="78"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="69"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="72"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="78"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="69"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="69"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5745,7 +6481,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="5.39"/>
@@ -5765,7 +6501,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -5777,14 +6513,14 @@
       <c r="I1" s="27"/>
       <c r="J1" s="27"/>
     </row>
-    <row r="2" s="31" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -5792,98 +6528,114 @@
       <c r="H2" s="30"/>
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="52"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="52"/>
+      <c r="H7" s="57"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="57"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="52"/>
+      <c r="H9" s="57"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="73"/>
+      <c r="H10" s="79"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
     </row>
@@ -5891,10 +6643,10 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="61" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="37"/>
@@ -5908,20 +6660,20 @@
         <v>1</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
     </row>
@@ -5930,20 +6682,20 @@
         <v>2</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="13"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="15"/>
       <c r="J14" s="14"/>
     </row>
@@ -5952,20 +6704,20 @@
         <v>3</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D15" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>25</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>26</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="13"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
     </row>
@@ -5974,20 +6726,20 @@
         <v>4</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>139</v>
+        <v>142</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>143</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="58"/>
       <c r="I16" s="15"/>
       <c r="J16" s="14"/>
     </row>
@@ -5996,20 +6748,20 @@
         <v>5</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="15"/>
       <c r="J17" s="14"/>
     </row>
@@ -6018,20 +6770,20 @@
         <v>6</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="15"/>
       <c r="J18" s="14"/>
     </row>
@@ -6039,21 +6791,21 @@
       <c r="A19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>144</v>
+      <c r="B19" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>148</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="15"/>
       <c r="J19" s="14"/>
     </row>
@@ -6061,21 +6813,21 @@
       <c r="A20" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>145</v>
+      <c r="B20" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>149</v>
       </c>
       <c r="D20" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="13"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="15"/>
       <c r="J20" s="14"/>
     </row>
@@ -6084,20 +6836,20 @@
         <v>9</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="13"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="15"/>
       <c r="J21" s="14"/>
     </row>
@@ -6106,20 +6858,20 @@
         <v>10</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="13"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="15"/>
       <c r="J22" s="14"/>
     </row>
@@ -6128,20 +6880,20 @@
         <v>11</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="13"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="58"/>
       <c r="I23" s="15"/>
       <c r="J23" s="14"/>
     </row>
@@ -6150,20 +6902,20 @@
         <v>12</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D24" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="13"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="15"/>
       <c r="J24" s="14"/>
     </row>
@@ -6172,20 +6924,20 @@
         <v>13</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D25" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="53"/>
+      <c r="H25" s="58"/>
       <c r="I25" s="15"/>
       <c r="J25" s="14"/>
     </row>
@@ -6194,20 +6946,20 @@
         <v>14</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D26" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>26</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="13"/>
-      <c r="H26" s="53"/>
+      <c r="H26" s="58"/>
       <c r="I26" s="15"/>
       <c r="J26" s="14"/>
     </row>
@@ -6216,20 +6968,20 @@
         <v>15</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="15"/>
       <c r="J27" s="14"/>
     </row>
@@ -6271,7 +7023,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -6290,7 +7042,7 @@
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -6303,12 +7055,12 @@
       <c r="A3" s="5"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="74"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10"/>
     </row>
@@ -6316,89 +7068,89 @@
       <c r="A4" s="5"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="74"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="75"/>
+      <c r="H5" s="81"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="74"/>
+      <c r="H6" s="80"/>
       <c r="I6" s="11"/>
       <c r="J6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="74"/>
+      <c r="H7" s="80"/>
       <c r="I7" s="11"/>
       <c r="J7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="74"/>
+      <c r="H8" s="80"/>
       <c r="I8" s="11"/>
       <c r="J8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="74"/>
+      <c r="H9" s="80"/>
       <c r="I9" s="11"/>
       <c r="J9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="76"/>
+      <c r="H10" s="82"/>
       <c r="I10" s="19"/>
       <c r="J10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="77"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="78"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="19"/>
       <c r="J11" s="18"/>
     </row>
@@ -6406,7 +7158,7 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="85" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="30" t="s">
@@ -6419,177 +7171,177 @@
       <c r="J12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80" t="n">
+      <c r="A13" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="82" t="s">
+      <c r="B13" s="87" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="90" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="83" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="84" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="57" t="s">
+      <c r="E15" s="63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="58" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="90" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="90" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="90" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="63" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="84" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="57" t="s">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="90" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="62" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="C16" s="84" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="80" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="84" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="40" t="s">
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="91" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="93" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="80" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="84" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="84" t="s">
-        <v>161</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="80" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="84" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="84" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="80" t="n">
-        <v>8</v>
-      </c>
-      <c r="B20" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="84" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="58" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="80" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="85" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="87" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="80" t="n">
+      <c r="A22" s="86" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="88" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="88" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="90" t="s">
-        <v>88</v>
+      <c r="B22" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="96" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="91"/>
+      <c r="A23" s="97"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -6843,7 +7595,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -6862,7 +7614,7 @@
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -6875,12 +7627,12 @@
       <c r="A3" s="5"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="74"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10"/>
     </row>
@@ -6888,89 +7640,89 @@
       <c r="A4" s="5"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="74"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="75"/>
+      <c r="H5" s="81"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="74"/>
+      <c r="H6" s="80"/>
       <c r="I6" s="11"/>
       <c r="J6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="74"/>
+      <c r="H7" s="80"/>
       <c r="I7" s="11"/>
       <c r="J7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="74"/>
+      <c r="H8" s="80"/>
       <c r="I8" s="11"/>
       <c r="J8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="74"/>
+      <c r="H9" s="80"/>
       <c r="I9" s="11"/>
       <c r="J9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="76"/>
+      <c r="H10" s="82"/>
       <c r="I10" s="19"/>
       <c r="J10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="78"/>
+      <c r="H11" s="84"/>
       <c r="I11" s="19"/>
       <c r="J11" s="18"/>
     </row>
@@ -6978,343 +7730,343 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="85" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="92"/>
+      <c r="F12" s="98"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80" t="n">
+      <c r="A13" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="93" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="83" t="s">
+      <c r="B13" s="99" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="99" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="101" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="101" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="94" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="102" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="57" t="s">
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="101" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="39" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="39" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="101" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" s="101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="39" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" s="101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="102" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="80" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="96" t="s">
+      <c r="E25" s="103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="86" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="104" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="102" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="104" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="86" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="80" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="95" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="95" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="97" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="104" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="104" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="104" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="104" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="96" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="80" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="98" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="D19" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="96" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="80" t="n">
-        <v>8</v>
-      </c>
-      <c r="B20" s="95" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>166</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="80" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" s="95" t="s">
-        <v>167</v>
-      </c>
-      <c r="C21" s="99" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="100" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="86" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="80" t="n">
-        <v>10</v>
-      </c>
-      <c r="B22" s="95" t="s">
-        <v>169</v>
-      </c>
-      <c r="C22" s="95" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="96" t="s">
+      <c r="B31" s="104" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="107" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="103" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="80" t="n">
-        <v>11</v>
-      </c>
-      <c r="B23" s="95" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="80" t="n">
-        <v>12</v>
-      </c>
-      <c r="B24" s="95" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="97" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="80" t="n">
-        <v>13</v>
-      </c>
-      <c r="B25" s="98" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="98" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="96" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="97" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="80" t="n">
-        <v>14</v>
-      </c>
-      <c r="B26" s="98" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="98" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="96" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="80" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="98" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" s="98" t="s">
-        <v>174</v>
-      </c>
-      <c r="D27" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="96" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="80" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="98" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="96" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="80" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="98" t="s">
-        <v>175</v>
-      </c>
-      <c r="C29" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="96" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="80" t="n">
-        <v>18</v>
-      </c>
-      <c r="B30" s="98" t="s">
-        <v>177</v>
-      </c>
-      <c r="C30" s="98" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="96" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="80" t="n">
-        <v>19</v>
-      </c>
-      <c r="B31" s="98" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="101" t="s">
-        <v>180</v>
-      </c>
-      <c r="D31" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="97" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="91"/>
+      <c r="A32" s="97"/>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -7568,7 +8320,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -7587,7 +8339,7 @@
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="30" t="s">
         <v>2</v>
       </c>
@@ -7600,12 +8352,12 @@
       <c r="A3" s="5"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="52"/>
+      <c r="H3" s="57"/>
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
     </row>
@@ -7613,89 +8365,89 @@
       <c r="A4" s="5"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="56" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="57"/>
       <c r="I4" s="15"/>
       <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="15"/>
       <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="56" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="52"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="15"/>
       <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="56" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="52"/>
+      <c r="H7" s="57"/>
       <c r="I7" s="15"/>
       <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="56" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="57"/>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="56" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="52"/>
+      <c r="H9" s="57"/>
       <c r="I9" s="15"/>
       <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="56" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="73"/>
+      <c r="H10" s="79"/>
       <c r="I10" s="21"/>
       <c r="J10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="77"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="54"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="21"/>
       <c r="J11" s="20"/>
     </row>
@@ -7703,190 +8455,190 @@
       <c r="A12" s="36"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="85" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="92"/>
+      <c r="F12" s="98"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80" t="n">
+      <c r="A13" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="108" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="109" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="104" t="s">
+      <c r="D13" s="110" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="105" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80" t="n">
+      <c r="A14" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="106" t="s">
+      <c r="B14" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="D14" s="108" t="s">
+      <c r="D14" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="109" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="80" t="n">
+      <c r="A15" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="106" t="s">
+      <c r="B15" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="107" t="s">
+      <c r="C15" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="109" t="s">
+      <c r="D15" s="115" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="108" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="80" t="n">
+      <c r="A16" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="112" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="107" t="s">
+      <c r="C16" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="D16" s="108" t="s">
+      <c r="D16" s="114" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="112" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="86" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="112" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="113" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="109" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="80" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="106" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="107" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="108" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="109" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="80" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="106" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="107" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="109" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="112" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="113" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="108" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="80" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="106" t="s">
+      <c r="E19" s="114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="C19" s="107" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="109" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="108" t="s">
+      <c r="C20" s="113" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="112" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="113" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="114" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="80" t="n">
-        <v>8</v>
-      </c>
-      <c r="B20" s="106" t="s">
+      <c r="E21" s="115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="116" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="117" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="107" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="109" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="108" t="s">
+      <c r="C22" s="118" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="119" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="80" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" s="106" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="D21" s="108" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="109" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="110" t="n">
-        <v>10</v>
-      </c>
-      <c r="B22" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="112" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="114" t="s">
-        <v>25</v>
+      <c r="E22" s="120" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="91"/>
+      <c r="A23" s="97"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>

--- a/static/esempio_paziente_completo.xlsx
+++ b/static/esempio_paziente_completo.xlsx
@@ -711,11 +711,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="2" style="2" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="23.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="21.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="21.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="26" style="0" width="23.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,6 +779,11 @@
       <c r="T3" s="7"/>
       <c r="U3" s="8"/>
       <c r="V3" s="9"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="11"/>
     </row>
     <row r="4" s="26" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
@@ -801,6 +810,11 @@
       <c r="T4" s="17"/>
       <c r="U4" s="18"/>
       <c r="V4" s="19"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="18"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
@@ -827,6 +841,11 @@
       <c r="T5" s="27"/>
       <c r="U5" s="28"/>
       <c r="V5" s="29"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36" t="s">
@@ -853,6 +872,11 @@
       <c r="T6" s="27"/>
       <c r="U6" s="28"/>
       <c r="V6" s="29"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
@@ -879,6 +903,11 @@
       <c r="T7" s="27"/>
       <c r="U7" s="28"/>
       <c r="V7" s="29"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
@@ -905,6 +934,11 @@
       <c r="T8" s="7"/>
       <c r="U8" s="8"/>
       <c r="V8" s="9"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -931,6 +965,11 @@
       <c r="T9" s="7"/>
       <c r="U9" s="8"/>
       <c r="V9" s="9"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
@@ -957,6 +996,11 @@
       <c r="T10" s="7"/>
       <c r="U10" s="8"/>
       <c r="V10" s="9"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
@@ -983,6 +1027,11 @@
       <c r="T11" s="7"/>
       <c r="U11" s="8"/>
       <c r="V11" s="9"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
@@ -1009,6 +1058,11 @@
       <c r="T12" s="37"/>
       <c r="U12" s="38"/>
       <c r="V12" s="39"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
@@ -1035,6 +1089,11 @@
       <c r="T13" s="46"/>
       <c r="U13" s="47"/>
       <c r="V13" s="48"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="47"/>
+      <c r="Y13" s="48"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="50"/>
     </row>
     <row r="14" s="64" customFormat="true" ht="51.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
@@ -1061,6 +1120,11 @@
       <c r="T14" s="55"/>
       <c r="U14" s="56"/>
       <c r="V14" s="57"/>
+      <c r="W14" s="55"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="58"/>
+      <c r="AA14" s="59"/>
     </row>
     <row r="15" s="64" customFormat="true" ht="24.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
@@ -1087,6 +1151,11 @@
       <c r="T15" s="65"/>
       <c r="U15" s="66"/>
       <c r="V15" s="67"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="67"/>
+      <c r="Z15" s="68"/>
+      <c r="AA15" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1094,19 +1163,19 @@
     <mergeCell ref="B2:V2"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B15 K15 T15" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B15 K15 T15 W15" type="list">
       <formula1>"Normale,DQ2.5 \ DQ2.5,DQ2.5 \ DQ2.2,DQ2.5 (cis),DQ2.5 (trans),DQ2.2 \ DQ2.2,DQ2.2 \ DQX,DQ8 \ DQ8,DQ8 \ DQX,DQ2.5 \ DQX,DQ2.5 \ DQ8,DQ7 \ DQX,DQ7 \ DQ7,DQ7 \ DQ2.2,DQ7 \ DQ8"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C15 L15 U15" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C15 L15 U15 X15" type="list">
       <formula1>"Normale,DQ2.5 \ DQ2.5,DQ2.5 \ DQ2.2,DQ2.5 (cis),DQ2.5 (trans),DQ2.2 \ DQ2.2,DQ2.2 \ DQX,DQ8 \ DQ8,DQ8 \ DQX,DQ2.5 \ DQX,DQ2.5 \ DQ8,DQ7 \ DQX,DQ7 \ DQ7,DQ7 \ DQ2.2,DQ7 \ DQ8"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D15:J15 M15:S15 V15" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D15:J15 M15:S15 V15 Y15:AA15" type="list">
       <formula1>"Normale,DQ2.5 \ DQ2.5,DQ2.5 \ DQ2.2,DQ2.5 (cis),DQ2.5 (trans),DQ2.2 \ DQ2.2,DQ2.2 \ DQX,DQ8 \ DQ8,DQ8 \ DQX,DQ2.5 \ DQX,DQ2.5 \ DQ8,DQ7 \ DQX,DQ7 \ DQ7,DQ7 \ DQ2.2,DQ7 \ DQ8"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B13:V13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B13:AA13" type="list">
       <formula1>"Altamedica,Genessere,Braincare,Longevia,IkonFiumicino,IkonAcilia,IkonCasalPalocco"</formula1>
       <formula2>0</formula2>
     </dataValidation>
